--- a/Emisiones/3.0 HV-HOJAS DE DATOS/P2437-IC-DTS-001 REV0.xlsx
+++ b/Emisiones/3.0 HV-HOJAS DE DATOS/P2437-IC-DTS-001 REV0.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.00000000000000"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -146,6 +146,11 @@
       <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -488,10 +493,10 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3218,7 +3223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O123"/>
+  <dimension ref="A1:O107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.61328125" customWidth="1" min="1" max="1"/>
@@ -3450,15 +3455,24 @@
           <t>Campo</t>
         </is>
       </c>
-      <c r="B10" s="59" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
+      <c r="B10" s="59" t="n"/>
       <c r="C10" s="59" t="n"/>
       <c r="D10" s="59" t="n"/>
       <c r="E10" s="59" t="n"/>
       <c r="F10" s="59" t="n"/>
+      <c r="G10" s="59" t="n"/>
+      <c r="H10" s="59" t="n"/>
+      <c r="I10" s="59" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="J10" s="59" t="n"/>
+      <c r="K10" s="59" t="n"/>
+      <c r="L10" s="59" t="n"/>
+      <c r="M10" s="59" t="n"/>
+      <c r="N10" s="59" t="n"/>
+      <c r="O10" s="59" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="60" t="inlineStr">
@@ -3466,15 +3480,24 @@
           <t>Código</t>
         </is>
       </c>
-      <c r="B11" s="60" t="inlineStr">
-        <is>
-          <t>HD-INST-001</t>
-        </is>
-      </c>
+      <c r="B11" s="61" t="n"/>
       <c r="C11" s="61" t="n"/>
       <c r="D11" s="61" t="n"/>
       <c r="E11" s="61" t="n"/>
       <c r="F11" s="61" t="n"/>
+      <c r="G11" s="61" t="n"/>
+      <c r="H11" s="61" t="n"/>
+      <c r="I11" s="60" t="inlineStr">
+        <is>
+          <t>HD-INST-001</t>
+        </is>
+      </c>
+      <c r="J11" s="61" t="n"/>
+      <c r="K11" s="61" t="n"/>
+      <c r="L11" s="61" t="n"/>
+      <c r="M11" s="61" t="n"/>
+      <c r="N11" s="61" t="n"/>
+      <c r="O11" s="61" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="60" t="inlineStr">
@@ -3482,15 +3505,24 @@
           <t>Revisión</t>
         </is>
       </c>
-      <c r="B12" s="60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="B12" s="61" t="n"/>
       <c r="C12" s="61" t="n"/>
       <c r="D12" s="61" t="n"/>
       <c r="E12" s="61" t="n"/>
       <c r="F12" s="61" t="n"/>
+      <c r="G12" s="61" t="n"/>
+      <c r="H12" s="61" t="n"/>
+      <c r="I12" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J12" s="61" t="n"/>
+      <c r="K12" s="61" t="n"/>
+      <c r="L12" s="61" t="n"/>
+      <c r="M12" s="61" t="n"/>
+      <c r="N12" s="61" t="n"/>
+      <c r="O12" s="61" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="60" t="inlineStr">
@@ -3498,15 +3530,24 @@
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B13" s="60" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
+      <c r="B13" s="61" t="n"/>
       <c r="C13" s="61" t="n"/>
       <c r="D13" s="61" t="n"/>
       <c r="E13" s="61" t="n"/>
       <c r="F13" s="61" t="n"/>
+      <c r="G13" s="61" t="n"/>
+      <c r="H13" s="61" t="n"/>
+      <c r="I13" s="60" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="J13" s="61" t="n"/>
+      <c r="K13" s="61" t="n"/>
+      <c r="L13" s="61" t="n"/>
+      <c r="M13" s="61" t="n"/>
+      <c r="N13" s="61" t="n"/>
+      <c r="O13" s="61" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="60" t="inlineStr">
@@ -3514,15 +3555,24 @@
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B14" s="60" t="inlineStr">
-        <is>
-          <t>P2437-HV-INF-001 — BRINSA, laboratorio de análisis industrial, Cajicá</t>
-        </is>
-      </c>
+      <c r="B14" s="61" t="n"/>
       <c r="C14" s="61" t="n"/>
       <c r="D14" s="61" t="n"/>
       <c r="E14" s="61" t="n"/>
       <c r="F14" s="61" t="n"/>
+      <c r="G14" s="61" t="n"/>
+      <c r="H14" s="61" t="n"/>
+      <c r="I14" s="60" t="inlineStr">
+        <is>
+          <t>P2437-HV-INF-001 — BRINSA, laboratorio de análisis industrial, Cajicá</t>
+        </is>
+      </c>
+      <c r="J14" s="61" t="n"/>
+      <c r="K14" s="61" t="n"/>
+      <c r="L14" s="61" t="n"/>
+      <c r="M14" s="61" t="n"/>
+      <c r="N14" s="61" t="n"/>
+      <c r="O14" s="61" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="60" t="inlineStr">
@@ -3530,15 +3580,24 @@
           <t>Etiquetas</t>
         </is>
       </c>
-      <c r="B15" s="60" t="inlineStr">
-        <is>
-          <t>PDT-001 (transmisor), PDI-001 (indicador local), PDSV-001 (damper de alivio barométrico)</t>
-        </is>
-      </c>
+      <c r="B15" s="61" t="n"/>
       <c r="C15" s="61" t="n"/>
       <c r="D15" s="61" t="n"/>
       <c r="E15" s="61" t="n"/>
       <c r="F15" s="61" t="n"/>
+      <c r="G15" s="61" t="n"/>
+      <c r="H15" s="61" t="n"/>
+      <c r="I15" s="60" t="inlineStr">
+        <is>
+          <t>PDT-001 (transmisor), PDI-001 (indicador local), PDSV-001 (damper de alivio barométrico)</t>
+        </is>
+      </c>
+      <c r="J15" s="61" t="n"/>
+      <c r="K15" s="61" t="n"/>
+      <c r="L15" s="61" t="n"/>
+      <c r="M15" s="61" t="n"/>
+      <c r="N15" s="61" t="n"/>
+      <c r="O15" s="61" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="62" t="inlineStr">
@@ -3556,784 +3615,1100 @@
     </row>
     <row r="20"/>
     <row r="21"/>
-    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="62" t="inlineStr">
+        <is>
+          <t>2. Arquitectura del lazo</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
-      <c r="A24" s="62" t="inlineStr">
-        <is>
-          <t>2. Arquitectura del lazo</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="63" t="inlineStr">
+      <c r="A24" s="63" t="inlineStr">
         <is>
           <t>2.1. Secuencia: el transmisor PDT-001 mide el diferencial interior–exterior y entrega 4-20 mA al PLC/BMS del cliente (o a relés autónomos); el indicador local PDI-001 permite verificación visual continua; el elemento final de control es el damper barométrico PDSV-001, cuyo contrapeso se calibra para abrir cuando el diferencial supera +25 Pa, descargando el exceso de caudal y estabilizando la presión de sala. Con filtro limpio (ΔP total 95 Pa en el sitio) el damper trabaja más abierto; con filtro cargado (190 Pa en el sitio) cierra y mantiene la consigna — compensación pasiva que hace al damper obligatorio (informe_investigacion.md §5.2).</t>
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26"/>
     <row r="27"/>
     <row r="28"/>
     <row r="29"/>
-    <row r="30"/>
+    <row r="30">
+      <c r="A30" s="63" t="inlineStr">
+        <is>
+          <t>2.2. El esquema corresponde al lazo documentado para presurización de edificios: sensor diferencial interior–exterior supervisando el elemento de alivio (Trane ADM-APN003 (https://www.trane.com/content/dam/Trane/Commercial/global/products-systems/education-training/engineers-newsletters/airside-design/admapn003en_0502.pdf), consulta 2026-07-23). Dado que el contrapeso actúa sobre diferencial de presión y no sobre caudal, el ajuste a +25 Pa es válido a la altitud del sitio; la posición de equilibrio cambia con la densidad, por lo que la calibración final se realiza en comisionamiento con micromanómetro (práctica documentada por Halton BRD (https://www.halton.com/app/uploads/2020/08/Halton-BRD-datasheet-2024.pdf), consulta 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
     <row r="31"/>
     <row r="32"/>
     <row r="33"/>
-    <row r="34">
-      <c r="A34" s="63" t="inlineStr">
-        <is>
-          <t>2.2. El esquema corresponde al lazo documentado para presurización de edificios: sensor diferencial interior–exterior supervisando el elemento de alivio (Trane ADM-APN003 (https://www.trane.com/content/dam/Trane/Commercial/global/products-systems/education-training/engineers-newsletters/airside-design/admapn003en_0502.pdf), consulta 2026-07-23). Dado que el contrapeso actúa sobre diferencial de presión y no sobre caudal, el ajuste a +25 Pa es válido a la altitud del sitio; la posición de equilibrio cambia con la densidad, por lo que la calibración final se realiza en comisionamiento con micromanómetro (práctica documentada por Halton BRD (https://www.halton.com/app/uploads/2020/08/Halton-BRD-datasheet-2024.pdf), consulta 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
+    <row r="34"/>
     <row r="35"/>
     <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" s="64" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="64" t="inlineStr">
         <is>
           <t>Tabla 1. Puntos de consigna y alarmas.</t>
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="59" t="inlineStr">
+        <is>
+          <t>Parámetro</t>
+        </is>
+      </c>
+      <c r="B38" s="59" t="n"/>
+      <c r="C38" s="59" t="n"/>
+      <c r="D38" s="59" t="n"/>
+      <c r="E38" s="59" t="n"/>
+      <c r="F38" s="59" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="G38" s="59" t="n"/>
+      <c r="H38" s="59" t="n"/>
+      <c r="I38" s="59" t="n"/>
+      <c r="J38" s="59" t="n"/>
+      <c r="K38" s="59" t="inlineStr">
+        <is>
+          <t>Acción</t>
+        </is>
+      </c>
+      <c r="L38" s="59" t="n"/>
+      <c r="M38" s="59" t="n"/>
+      <c r="N38" s="59" t="n"/>
+      <c r="O38" s="59" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="60" t="inlineStr">
+        <is>
+          <t>Set-point de presurización</t>
+        </is>
+      </c>
+      <c r="B39" s="61" t="n"/>
+      <c r="C39" s="61" t="n"/>
+      <c r="D39" s="61" t="n"/>
+      <c r="E39" s="61" t="n"/>
+      <c r="F39" s="60" t="inlineStr">
+        <is>
+          <t>+25 Pa</t>
+        </is>
+      </c>
+      <c r="G39" s="61" t="n"/>
+      <c r="H39" s="61" t="n"/>
+      <c r="I39" s="61" t="n"/>
+      <c r="J39" s="61" t="n"/>
+      <c r="K39" s="60" t="inlineStr">
+        <is>
+          <t>Ajuste del contrapeso del damper PDSV-001</t>
+        </is>
+      </c>
+      <c r="L39" s="61" t="n"/>
+      <c r="M39" s="61" t="n"/>
+      <c r="N39" s="61" t="n"/>
+      <c r="O39" s="61" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="60" t="inlineStr">
+        <is>
+          <t>Alarma baja</t>
+        </is>
+      </c>
+      <c r="B40" s="61" t="n"/>
+      <c r="C40" s="61" t="n"/>
+      <c r="D40" s="61" t="n"/>
+      <c r="E40" s="61" t="n"/>
+      <c r="F40" s="60" t="inlineStr">
+        <is>
+          <t>+12.5 Pa</t>
+        </is>
+      </c>
+      <c r="G40" s="61" t="n"/>
+      <c r="H40" s="61" t="n"/>
+      <c r="I40" s="61" t="n"/>
+      <c r="J40" s="61" t="n"/>
+      <c r="K40" s="60" t="inlineStr">
+        <is>
+          <t>Pérdida de presurización: riesgo de ingreso de insectos, polvo y cloro</t>
+        </is>
+      </c>
+      <c r="L40" s="61" t="n"/>
+      <c r="M40" s="61" t="n"/>
+      <c r="N40" s="61" t="n"/>
+      <c r="O40" s="61" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="60" t="inlineStr">
+        <is>
+          <t>Alarma alta</t>
+        </is>
+      </c>
+      <c r="B41" s="61" t="n"/>
+      <c r="C41" s="61" t="n"/>
+      <c r="D41" s="61" t="n"/>
+      <c r="E41" s="61" t="n"/>
+      <c r="F41" s="60" t="inlineStr">
+        <is>
+          <t>+40 Pa</t>
+        </is>
+      </c>
+      <c r="G41" s="61" t="n"/>
+      <c r="H41" s="61" t="n"/>
+      <c r="I41" s="61" t="n"/>
+      <c r="J41" s="61" t="n"/>
+      <c r="K41" s="60" t="inlineStr">
+        <is>
+          <t>Damper atascado o falla de exfiltración (dato típico)</t>
+        </is>
+      </c>
+      <c r="L41" s="61" t="n"/>
+      <c r="M41" s="61" t="n"/>
+      <c r="N41" s="61" t="n"/>
+      <c r="O41" s="61" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="60" t="inlineStr">
+        <is>
+          <t>Retardo de alarmas</t>
+        </is>
+      </c>
+      <c r="B42" s="61" t="n"/>
+      <c r="C42" s="61" t="n"/>
+      <c r="D42" s="61" t="n"/>
+      <c r="E42" s="61" t="n"/>
+      <c r="F42" s="60" t="inlineStr">
+        <is>
+          <t>30-60 s</t>
+        </is>
+      </c>
+      <c r="G42" s="61" t="n"/>
+      <c r="H42" s="61" t="n"/>
+      <c r="I42" s="61" t="n"/>
+      <c r="J42" s="61" t="n"/>
+      <c r="K42" s="60" t="inlineStr">
+        <is>
+          <t>Evita falsas alarmas por apertura de puerta (dato típico)</t>
+        </is>
+      </c>
+      <c r="L42" s="61" t="n"/>
+      <c r="M42" s="61" t="n"/>
+      <c r="N42" s="61" t="n"/>
+      <c r="O42" s="61" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="60" t="inlineStr">
+        <is>
+          <t>Límite superior absoluto</t>
+        </is>
+      </c>
+      <c r="B43" s="61" t="n"/>
+      <c r="C43" s="61" t="n"/>
+      <c r="D43" s="61" t="n"/>
+      <c r="E43" s="61" t="n"/>
+      <c r="F43" s="60" t="inlineStr">
+        <is>
+          <t>≈60 Pa</t>
+        </is>
+      </c>
+      <c r="G43" s="61" t="n"/>
+      <c r="H43" s="61" t="n"/>
+      <c r="I43" s="61" t="n"/>
+      <c r="J43" s="61" t="n"/>
+      <c r="K43" s="60" t="inlineStr">
+        <is>
+          <t>Fuerza de apertura de puertas (referencia IBC 1009.3; dato típico)</t>
+        </is>
+      </c>
+      <c r="L43" s="61" t="n"/>
+      <c r="M43" s="61" t="n"/>
+      <c r="N43" s="61" t="n"/>
+      <c r="O43" s="61" t="n"/>
+    </row>
     <row r="45">
-      <c r="A45" s="59" t="inlineStr">
+      <c r="A45" s="63" t="inlineStr">
+        <is>
+          <t>2.3. El lazo activo (variador de frecuencia o damper motorizado) solo se justifica con aperturas frecuentes de puerta o exigencia de registro BMS (AIVC airbase_7469 (PDF) (https://www.aivc.org/sites/default/files/airbase_7469.pdf), consulta 2026-07-23); para el set-point fijo de este proyecto se adopta la solución pasiva de máxima confiabilidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="49">
+      <c r="A49" s="62" t="inlineStr">
+        <is>
+          <t>3. Transmisor de presión diferencial (PDT-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="64" t="inlineStr">
+        <is>
+          <t>Tabla 2. Especificación y candidatos (consulta 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="59" t="inlineStr">
         <is>
           <t>Parámetro</t>
         </is>
       </c>
-      <c r="B45" s="59" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="C45" s="59" t="inlineStr">
-        <is>
-          <t>Acción</t>
-        </is>
-      </c>
-      <c r="D45" s="59" t="n"/>
-      <c r="E45" s="59" t="n"/>
-      <c r="F45" s="59" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="60" t="inlineStr">
-        <is>
-          <t>Set-point de presurización</t>
-        </is>
-      </c>
-      <c r="B46" s="60" t="inlineStr">
-        <is>
-          <t>+25 Pa</t>
-        </is>
-      </c>
-      <c r="C46" s="60" t="inlineStr">
-        <is>
-          <t>Ajuste del contrapeso del damper PDSV-001</t>
-        </is>
-      </c>
-      <c r="D46" s="61" t="n"/>
-      <c r="E46" s="61" t="n"/>
-      <c r="F46" s="61" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="60" t="inlineStr">
-        <is>
-          <t>Alarma baja</t>
-        </is>
-      </c>
-      <c r="B47" s="60" t="inlineStr">
-        <is>
-          <t>+12.5 Pa</t>
-        </is>
-      </c>
-      <c r="C47" s="60" t="inlineStr">
-        <is>
-          <t>Pérdida de presurización: riesgo de ingreso de insectos, polvo y cloro</t>
-        </is>
-      </c>
-      <c r="D47" s="61" t="n"/>
-      <c r="E47" s="61" t="n"/>
-      <c r="F47" s="61" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="60" t="inlineStr">
-        <is>
-          <t>Alarma alta</t>
-        </is>
-      </c>
-      <c r="B48" s="60" t="inlineStr">
-        <is>
-          <t>+40 Pa</t>
-        </is>
-      </c>
-      <c r="C48" s="60" t="inlineStr">
-        <is>
-          <t>Damper atascado o falla de exfiltración (dato típico)</t>
-        </is>
-      </c>
-      <c r="D48" s="61" t="n"/>
-      <c r="E48" s="61" t="n"/>
-      <c r="F48" s="61" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="60" t="inlineStr">
-        <is>
-          <t>Retardo de alarmas</t>
-        </is>
-      </c>
-      <c r="B49" s="60" t="inlineStr">
-        <is>
-          <t>30-60 s</t>
-        </is>
-      </c>
-      <c r="C49" s="60" t="inlineStr">
-        <is>
-          <t>Evita falsas alarmas por apertura de puerta (dato típico)</t>
-        </is>
-      </c>
-      <c r="D49" s="61" t="n"/>
-      <c r="E49" s="61" t="n"/>
-      <c r="F49" s="61" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="60" t="inlineStr">
-        <is>
-          <t>Límite superior absoluto</t>
-        </is>
-      </c>
-      <c r="B50" s="60" t="inlineStr">
-        <is>
-          <t>≈60 Pa</t>
-        </is>
-      </c>
-      <c r="C50" s="60" t="inlineStr">
-        <is>
-          <t>Fuerza de apertura de puertas (referencia IBC 1009.3; dato típico)</t>
-        </is>
-      </c>
-      <c r="D50" s="61" t="n"/>
-      <c r="E50" s="61" t="n"/>
-      <c r="F50" s="61" t="n"/>
+      <c r="B51" s="59" t="n"/>
+      <c r="C51" s="59" t="n"/>
+      <c r="D51" s="59" t="n"/>
+      <c r="E51" s="59" t="n"/>
+      <c r="F51" s="59" t="n"/>
+      <c r="G51" s="59" t="n"/>
+      <c r="H51" s="59" t="n"/>
+      <c r="I51" s="59" t="inlineStr">
+        <is>
+          <t>Especificación / candidatos</t>
+        </is>
+      </c>
+      <c r="J51" s="59" t="n"/>
+      <c r="K51" s="59" t="n"/>
+      <c r="L51" s="59" t="n"/>
+      <c r="M51" s="59" t="n"/>
+      <c r="N51" s="59" t="n"/>
+      <c r="O51" s="59" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="63" t="inlineStr">
-        <is>
-          <t>2.3. El lazo activo (variador de frecuencia o damper motorizado) solo se justifica con aperturas frecuentes de puerta o exigencia de registro BMS (AIVC airbase_7469 (PDF) (https://www.aivc.org/sites/default/files/airbase_7469.pdf), consulta 2026-07-23); para el set-point fijo de este proyecto se adopta la solución pasiva de máxima confiabilidad.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
+      <c r="A52" s="60" t="inlineStr">
+        <is>
+          <t>Rango</t>
+        </is>
+      </c>
+      <c r="B52" s="61" t="n"/>
+      <c r="C52" s="61" t="n"/>
+      <c r="D52" s="61" t="n"/>
+      <c r="E52" s="61" t="n"/>
+      <c r="F52" s="61" t="n"/>
+      <c r="G52" s="61" t="n"/>
+      <c r="H52" s="61" t="n"/>
+      <c r="I52" s="60" t="inlineStr">
+        <is>
+          <t>0-62.5 Pa (0-0.25 in c.a.); set-point al 40 % de escala</t>
+        </is>
+      </c>
+      <c r="J52" s="61" t="n"/>
+      <c r="K52" s="61" t="n"/>
+      <c r="L52" s="61" t="n"/>
+      <c r="M52" s="61" t="n"/>
+      <c r="N52" s="61" t="n"/>
+      <c r="O52" s="61" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="60" t="inlineStr">
+        <is>
+          <t>Salida</t>
+        </is>
+      </c>
+      <c r="B53" s="61" t="n"/>
+      <c r="C53" s="61" t="n"/>
+      <c r="D53" s="61" t="n"/>
+      <c r="E53" s="61" t="n"/>
+      <c r="F53" s="61" t="n"/>
+      <c r="G53" s="61" t="n"/>
+      <c r="H53" s="61" t="n"/>
+      <c r="I53" s="60" t="inlineStr">
+        <is>
+          <t>4-20 mA, 2 hilos</t>
+        </is>
+      </c>
+      <c r="J53" s="61" t="n"/>
+      <c r="K53" s="61" t="n"/>
+      <c r="L53" s="61" t="n"/>
+      <c r="M53" s="61" t="n"/>
+      <c r="N53" s="61" t="n"/>
+      <c r="O53" s="61" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="60" t="inlineStr">
+        <is>
+          <t>Precisión</t>
+        </is>
+      </c>
+      <c r="B54" s="61" t="n"/>
+      <c r="C54" s="61" t="n"/>
+      <c r="D54" s="61" t="n"/>
+      <c r="E54" s="61" t="n"/>
+      <c r="F54" s="61" t="n"/>
+      <c r="G54" s="61" t="n"/>
+      <c r="H54" s="61" t="n"/>
+      <c r="I54" s="60" t="inlineStr">
+        <is>
+          <t>±1 % FS o mejor</t>
+        </is>
+      </c>
+      <c r="J54" s="61" t="n"/>
+      <c r="K54" s="61" t="n"/>
+      <c r="L54" s="61" t="n"/>
+      <c r="M54" s="61" t="n"/>
+      <c r="N54" s="61" t="n"/>
+      <c r="O54" s="61" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="60" t="inlineStr">
+        <is>
+          <t>Protección</t>
+        </is>
+      </c>
+      <c r="B55" s="61" t="n"/>
+      <c r="C55" s="61" t="n"/>
+      <c r="D55" s="61" t="n"/>
+      <c r="E55" s="61" t="n"/>
+      <c r="F55" s="61" t="n"/>
+      <c r="G55" s="61" t="n"/>
+      <c r="H55" s="61" t="n"/>
+      <c r="I55" s="60" t="inlineStr">
+        <is>
+          <t>NEMA 4X (IP66); montaje en interior, toma exterior protegida</t>
+        </is>
+      </c>
+      <c r="J55" s="61" t="n"/>
+      <c r="K55" s="61" t="n"/>
+      <c r="L55" s="61" t="n"/>
+      <c r="M55" s="61" t="n"/>
+      <c r="N55" s="61" t="n"/>
+      <c r="O55" s="61" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="60" t="inlineStr">
+        <is>
+          <t>Constante de tiempo</t>
+        </is>
+      </c>
+      <c r="B56" s="61" t="n"/>
+      <c r="C56" s="61" t="n"/>
+      <c r="D56" s="61" t="n"/>
+      <c r="E56" s="61" t="n"/>
+      <c r="F56" s="61" t="n"/>
+      <c r="G56" s="61" t="n"/>
+      <c r="H56" s="61" t="n"/>
+      <c r="I56" s="60" t="inlineStr">
+        <is>
+          <t>Ajustable 0.5-15 s (amortigua ráfagas de viento en la referencia)</t>
+        </is>
+      </c>
+      <c r="J56" s="61" t="n"/>
+      <c r="K56" s="61" t="n"/>
+      <c r="L56" s="61" t="n"/>
+      <c r="M56" s="61" t="n"/>
+      <c r="N56" s="61" t="n"/>
+      <c r="O56" s="61" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="60" t="inlineStr">
+        <is>
+          <t>Primera opción</t>
+        </is>
+      </c>
+      <c r="B57" s="61" t="n"/>
+      <c r="C57" s="61" t="n"/>
+      <c r="D57" s="61" t="n"/>
+      <c r="E57" s="61" t="n"/>
+      <c r="F57" s="61" t="n"/>
+      <c r="G57" s="61" t="n"/>
+      <c r="H57" s="61" t="n"/>
+      <c r="I57" s="60" t="inlineStr">
+        <is>
+          <t>Dwyer MS-121(-LCD) Magnesense: rangos seleccionables 25/62.5/125 Pa, ±1 % FS, NEMA 4X (catálogo (PDF) (https://www.transcat.com/media/pdf/MS_cat.pdf))</t>
+        </is>
+      </c>
+      <c r="J57" s="61" t="n"/>
+      <c r="K57" s="61" t="n"/>
+      <c r="L57" s="61" t="n"/>
+      <c r="M57" s="61" t="n"/>
+      <c r="N57" s="61" t="n"/>
+      <c r="O57" s="61" t="n"/>
+    </row>
     <row r="58">
-      <c r="A58" s="62" t="inlineStr">
-        <is>
-          <t>3. Transmisor de presión diferencial (PDT-001)</t>
-        </is>
-      </c>
+      <c r="A58" s="60" t="inlineStr">
+        <is>
+          <t>Alternativa premium</t>
+        </is>
+      </c>
+      <c r="B58" s="61" t="n"/>
+      <c r="C58" s="61" t="n"/>
+      <c r="D58" s="61" t="n"/>
+      <c r="E58" s="61" t="n"/>
+      <c r="F58" s="61" t="n"/>
+      <c r="G58" s="61" t="n"/>
+      <c r="H58" s="61" t="n"/>
+      <c r="I58" s="60" t="inlineStr">
+        <is>
+          <t>Setra 264, rango 0-0.25 in c.a., ±0.25/±0.4/±1 % FS, elemento capacitivo inox (datasheet (PDF) (https://www.setra.com/hubfs/Product_Data_Sheets/Setra_Model_264_Data_Sheet.pdf)); suministro por importación, por confirmar stock</t>
+        </is>
+      </c>
+      <c r="J58" s="61" t="n"/>
+      <c r="K58" s="61" t="n"/>
+      <c r="L58" s="61" t="n"/>
+      <c r="M58" s="61" t="n"/>
+      <c r="N58" s="61" t="n"/>
+      <c r="O58" s="61" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="64" t="inlineStr">
-        <is>
-          <t>Tabla 2. Especificación y candidatos (consulta 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="59" t="inlineStr">
+      <c r="A59" s="60" t="inlineStr">
+        <is>
+          <t>Alternativa BMS Siemens</t>
+        </is>
+      </c>
+      <c r="B59" s="61" t="n"/>
+      <c r="C59" s="61" t="n"/>
+      <c r="D59" s="61" t="n"/>
+      <c r="E59" s="61" t="n"/>
+      <c r="F59" s="61" t="n"/>
+      <c r="G59" s="61" t="n"/>
+      <c r="H59" s="61" t="n"/>
+      <c r="I59" s="60" t="inlineStr">
+        <is>
+          <t>Siemens QBM2130-1U, 0-100 Pa, 4-20 mA, IP42 (exige gabinete adicional) (Industry Mall (https://mall.industry.siemens.com/mall/en/WW/Catalog/Products/10510770))</t>
+        </is>
+      </c>
+      <c r="J59" s="61" t="n"/>
+      <c r="K59" s="61" t="n"/>
+      <c r="L59" s="61" t="n"/>
+      <c r="M59" s="61" t="n"/>
+      <c r="N59" s="61" t="n"/>
+      <c r="O59" s="61" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="62" t="inlineStr">
+        <is>
+          <t>4. Indicador local (PDI-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="64" t="inlineStr">
+        <is>
+          <t>Tabla 3. Especificación del manómetro diferencial (consulta 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="59" t="inlineStr">
         <is>
           <t>Parámetro</t>
         </is>
       </c>
-      <c r="B60" s="59" t="inlineStr">
-        <is>
-          <t>Especificación / candidatos</t>
-        </is>
-      </c>
-      <c r="C60" s="59" t="n"/>
-      <c r="D60" s="59" t="n"/>
-      <c r="E60" s="59" t="n"/>
-      <c r="F60" s="59" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="60" t="inlineStr">
-        <is>
-          <t>Rango</t>
-        </is>
-      </c>
-      <c r="B61" s="60" t="inlineStr">
-        <is>
-          <t>0-62.5 Pa (0-0.25 in c.a.); set-point al 40 % de escala</t>
-        </is>
-      </c>
-      <c r="C61" s="61" t="n"/>
-      <c r="D61" s="61" t="n"/>
-      <c r="E61" s="61" t="n"/>
-      <c r="F61" s="61" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="60" t="inlineStr">
-        <is>
-          <t>Salida</t>
-        </is>
-      </c>
-      <c r="B62" s="60" t="inlineStr">
-        <is>
-          <t>4-20 mA, 2 hilos</t>
-        </is>
-      </c>
-      <c r="C62" s="61" t="n"/>
-      <c r="D62" s="61" t="n"/>
-      <c r="E62" s="61" t="n"/>
-      <c r="F62" s="61" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="60" t="inlineStr">
-        <is>
-          <t>Precisión</t>
-        </is>
-      </c>
-      <c r="B63" s="60" t="inlineStr">
-        <is>
-          <t>±1 % FS o mejor</t>
-        </is>
-      </c>
-      <c r="C63" s="61" t="n"/>
-      <c r="D63" s="61" t="n"/>
-      <c r="E63" s="61" t="n"/>
-      <c r="F63" s="61" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="60" t="inlineStr">
-        <is>
-          <t>Protección</t>
-        </is>
-      </c>
-      <c r="B64" s="60" t="inlineStr">
-        <is>
-          <t>NEMA 4X (IP66); montaje en interior, toma exterior protegida</t>
-        </is>
-      </c>
-      <c r="C64" s="61" t="n"/>
-      <c r="D64" s="61" t="n"/>
-      <c r="E64" s="61" t="n"/>
-      <c r="F64" s="61" t="n"/>
+      <c r="B64" s="59" t="n"/>
+      <c r="C64" s="59" t="n"/>
+      <c r="D64" s="59" t="n"/>
+      <c r="E64" s="59" t="n"/>
+      <c r="F64" s="59" t="n"/>
+      <c r="G64" s="59" t="n"/>
+      <c r="H64" s="59" t="n"/>
+      <c r="I64" s="59" t="inlineStr">
+        <is>
+          <t>Especificación</t>
+        </is>
+      </c>
+      <c r="J64" s="59" t="n"/>
+      <c r="K64" s="59" t="n"/>
+      <c r="L64" s="59" t="n"/>
+      <c r="M64" s="59" t="n"/>
+      <c r="N64" s="59" t="n"/>
+      <c r="O64" s="59" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="60" t="inlineStr">
         <is>
-          <t>Constante de tiempo</t>
-        </is>
-      </c>
-      <c r="B65" s="60" t="inlineStr">
-        <is>
-          <t>Ajustable 0.5-15 s (amortigua ráfagas de viento en la referencia)</t>
-        </is>
-      </c>
+          <t>Modelo de referencia</t>
+        </is>
+      </c>
+      <c r="B65" s="61" t="n"/>
       <c r="C65" s="61" t="n"/>
       <c r="D65" s="61" t="n"/>
       <c r="E65" s="61" t="n"/>
       <c r="F65" s="61" t="n"/>
+      <c r="G65" s="61" t="n"/>
+      <c r="H65" s="61" t="n"/>
+      <c r="I65" s="60" t="inlineStr">
+        <is>
+          <t>Dwyer Magnehelic serie 2000, modelo 2000-00</t>
+        </is>
+      </c>
+      <c r="J65" s="61" t="n"/>
+      <c r="K65" s="61" t="n"/>
+      <c r="L65" s="61" t="n"/>
+      <c r="M65" s="61" t="n"/>
+      <c r="N65" s="61" t="n"/>
+      <c r="O65" s="61" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="60" t="inlineStr">
         <is>
-          <t>Primera opción</t>
-        </is>
-      </c>
-      <c r="B66" s="60" t="inlineStr">
-        <is>
-          <t>Dwyer MS-121(-LCD) Magnesense: rangos seleccionables 25/62.5/125 Pa, ±1 % FS, NEMA 4X (catálogo (PDF) (https://www.transcat.com/media/pdf/MS_cat.pdf))</t>
-        </is>
-      </c>
+          <t>Rango</t>
+        </is>
+      </c>
+      <c r="B66" s="61" t="n"/>
       <c r="C66" s="61" t="n"/>
       <c r="D66" s="61" t="n"/>
       <c r="E66" s="61" t="n"/>
       <c r="F66" s="61" t="n"/>
+      <c r="G66" s="61" t="n"/>
+      <c r="H66" s="61" t="n"/>
+      <c r="I66" s="60" t="inlineStr">
+        <is>
+          <t>0-62 Pa (0-0.25 in c.a.); división menor 0.005 in c.a.</t>
+        </is>
+      </c>
+      <c r="J66" s="61" t="n"/>
+      <c r="K66" s="61" t="n"/>
+      <c r="L66" s="61" t="n"/>
+      <c r="M66" s="61" t="n"/>
+      <c r="N66" s="61" t="n"/>
+      <c r="O66" s="61" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="60" t="inlineStr">
         <is>
-          <t>Alternativa premium</t>
-        </is>
-      </c>
-      <c r="B67" s="60" t="inlineStr">
-        <is>
-          <t>Setra 264, rango 0-0.25 in c.a., ±0.25/±0.4/±1 % FS, elemento capacitivo inox (datasheet (PDF) (https://www.setra.com/hubfs/Product_Data_Sheets/Setra_Model_264_Data_Sheet.pdf)); suministro por importación, por confirmar stock</t>
-        </is>
-      </c>
+          <t>Precisión</t>
+        </is>
+      </c>
+      <c r="B67" s="61" t="n"/>
       <c r="C67" s="61" t="n"/>
       <c r="D67" s="61" t="n"/>
       <c r="E67" s="61" t="n"/>
       <c r="F67" s="61" t="n"/>
+      <c r="G67" s="61" t="n"/>
+      <c r="H67" s="61" t="n"/>
+      <c r="I67" s="60" t="inlineStr">
+        <is>
+          <t>±2 % FS</t>
+        </is>
+      </c>
+      <c r="J67" s="61" t="n"/>
+      <c r="K67" s="61" t="n"/>
+      <c r="L67" s="61" t="n"/>
+      <c r="M67" s="61" t="n"/>
+      <c r="N67" s="61" t="n"/>
+      <c r="O67" s="61" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="60" t="inlineStr">
         <is>
-          <t>Alternativa BMS Siemens</t>
-        </is>
-      </c>
-      <c r="B68" s="60" t="inlineStr">
-        <is>
-          <t>Siemens QBM2130-1U, 0-100 Pa, 4-20 mA, IP42 (exige gabinete adicional) (Industry Mall (https://mall.industry.siemens.com/mall/en/WW/Catalog/Products/10510770))</t>
-        </is>
-      </c>
+          <t>Construcción</t>
+        </is>
+      </c>
+      <c r="B68" s="61" t="n"/>
       <c r="C68" s="61" t="n"/>
       <c r="D68" s="61" t="n"/>
       <c r="E68" s="61" t="n"/>
       <c r="F68" s="61" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="62" t="inlineStr">
-        <is>
-          <t>4. Indicador local (PDI-001)</t>
-        </is>
-      </c>
+      <c r="G68" s="61" t="n"/>
+      <c r="H68" s="61" t="n"/>
+      <c r="I68" s="60" t="inlineStr">
+        <is>
+          <t>Caja aluminio fundido (ensayo niebla salina 168 h); opción bisel inox (-SS); conexiones 1/8 in NPT</t>
+        </is>
+      </c>
+      <c r="J68" s="61" t="n"/>
+      <c r="K68" s="61" t="n"/>
+      <c r="L68" s="61" t="n"/>
+      <c r="M68" s="61" t="n"/>
+      <c r="N68" s="61" t="n"/>
+      <c r="O68" s="61" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="60" t="inlineStr">
+        <is>
+          <t>Montaje</t>
+        </is>
+      </c>
+      <c r="B69" s="61" t="n"/>
+      <c r="C69" s="61" t="n"/>
+      <c r="D69" s="61" t="n"/>
+      <c r="E69" s="61" t="n"/>
+      <c r="F69" s="61" t="n"/>
+      <c r="G69" s="61" t="n"/>
+      <c r="H69" s="61" t="n"/>
+      <c r="I69" s="60" t="inlineStr">
+        <is>
+          <t>Embutido en panel/puerta del laboratorio (interior)</t>
+        </is>
+      </c>
+      <c r="J69" s="61" t="n"/>
+      <c r="K69" s="61" t="n"/>
+      <c r="L69" s="61" t="n"/>
+      <c r="M69" s="61" t="n"/>
+      <c r="N69" s="61" t="n"/>
+      <c r="O69" s="61" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="60" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="B70" s="61" t="n"/>
+      <c r="C70" s="61" t="n"/>
+      <c r="D70" s="61" t="n"/>
+      <c r="E70" s="61" t="n"/>
+      <c r="F70" s="61" t="n"/>
+      <c r="G70" s="61" t="n"/>
+      <c r="H70" s="61" t="n"/>
+      <c r="I70" s="60" t="inlineStr">
+        <is>
+          <t>Skilltech — tabla serie 2000 (https://skilltech.com.br/produto/manometro-para-pressao-diferencial-magnehelic-serie-2000/)</t>
+        </is>
+      </c>
+      <c r="J70" s="61" t="n"/>
+      <c r="K70" s="61" t="n"/>
+      <c r="L70" s="61" t="n"/>
+      <c r="M70" s="61" t="n"/>
+      <c r="N70" s="61" t="n"/>
+      <c r="O70" s="61" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="64" t="inlineStr">
-        <is>
-          <t>Tabla 3. Especificación del manómetro diferencial (consulta 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="59" t="inlineStr">
+      <c r="A72" s="63" t="inlineStr">
+        <is>
+          <t>4.1. Si el cliente no dispone de PLC, se sustituye/complementa con Dwyer Photohelic 3000MR-00AV (indicador + 2 relés SPDT, rango 0-0.25 in c.a.; Northeast Controls (https://nciweb.net/pressure1.htm), consulta 2026-07-23), que genera las alarmas de la Tabla 1 de forma autónoma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="76">
+      <c r="A76" s="62" t="inlineStr">
+        <is>
+          <t>5. Damper de alivio barométrico (PDSV-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="64" t="inlineStr">
+        <is>
+          <t>Tabla 4. Especificación y candidatos (consulta 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="59" t="inlineStr">
         <is>
           <t>Parámetro</t>
         </is>
       </c>
-      <c r="B73" s="59" t="inlineStr">
-        <is>
-          <t>Especificación</t>
-        </is>
-      </c>
-      <c r="C73" s="59" t="n"/>
-      <c r="D73" s="59" t="n"/>
-      <c r="E73" s="59" t="n"/>
-      <c r="F73" s="59" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="60" t="inlineStr">
-        <is>
-          <t>Modelo de referencia</t>
-        </is>
-      </c>
-      <c r="B74" s="60" t="inlineStr">
-        <is>
-          <t>Dwyer Magnehelic serie 2000, modelo 2000-00</t>
-        </is>
-      </c>
-      <c r="C74" s="61" t="n"/>
-      <c r="D74" s="61" t="n"/>
-      <c r="E74" s="61" t="n"/>
-      <c r="F74" s="61" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="60" t="inlineStr">
-        <is>
-          <t>Rango</t>
-        </is>
-      </c>
-      <c r="B75" s="60" t="inlineStr">
-        <is>
-          <t>0-62 Pa (0-0.25 in c.a.); división menor 0.005 in c.a.</t>
-        </is>
-      </c>
-      <c r="C75" s="61" t="n"/>
-      <c r="D75" s="61" t="n"/>
-      <c r="E75" s="61" t="n"/>
-      <c r="F75" s="61" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="60" t="inlineStr">
-        <is>
-          <t>Precisión</t>
-        </is>
-      </c>
-      <c r="B76" s="60" t="inlineStr">
-        <is>
-          <t>±2 % FS</t>
-        </is>
-      </c>
-      <c r="C76" s="61" t="n"/>
-      <c r="D76" s="61" t="n"/>
-      <c r="E76" s="61" t="n"/>
-      <c r="F76" s="61" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="60" t="inlineStr">
-        <is>
-          <t>Construcción</t>
-        </is>
-      </c>
-      <c r="B77" s="60" t="inlineStr">
-        <is>
-          <t>Caja aluminio fundido (ensayo niebla salina 168 h); opción bisel inox (-SS); conexiones 1/8 in NPT</t>
-        </is>
-      </c>
-      <c r="C77" s="61" t="n"/>
-      <c r="D77" s="61" t="n"/>
-      <c r="E77" s="61" t="n"/>
-      <c r="F77" s="61" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="60" t="inlineStr">
-        <is>
-          <t>Montaje</t>
-        </is>
-      </c>
-      <c r="B78" s="60" t="inlineStr">
-        <is>
-          <t>Embutido en panel/puerta del laboratorio (interior)</t>
-        </is>
-      </c>
-      <c r="C78" s="61" t="n"/>
-      <c r="D78" s="61" t="n"/>
-      <c r="E78" s="61" t="n"/>
-      <c r="F78" s="61" t="n"/>
+      <c r="B78" s="59" t="n"/>
+      <c r="C78" s="59" t="n"/>
+      <c r="D78" s="59" t="n"/>
+      <c r="E78" s="59" t="n"/>
+      <c r="F78" s="59" t="n"/>
+      <c r="G78" s="59" t="n"/>
+      <c r="H78" s="59" t="n"/>
+      <c r="I78" s="59" t="inlineStr">
+        <is>
+          <t>Especificación / candidatos</t>
+        </is>
+      </c>
+      <c r="J78" s="59" t="n"/>
+      <c r="K78" s="59" t="n"/>
+      <c r="L78" s="59" t="n"/>
+      <c r="M78" s="59" t="n"/>
+      <c r="N78" s="59" t="n"/>
+      <c r="O78" s="59" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="60" t="inlineStr">
         <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="B79" s="60" t="inlineStr">
-        <is>
-          <t>Skilltech — tabla serie 2000 (https://skilltech.com.br/produto/manometro-para-pressao-diferencial-magnehelic-serie-2000/)</t>
-        </is>
-      </c>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B79" s="61" t="n"/>
       <c r="C79" s="61" t="n"/>
       <c r="D79" s="61" t="n"/>
       <c r="E79" s="61" t="n"/>
       <c r="F79" s="61" t="n"/>
+      <c r="G79" s="61" t="n"/>
+      <c r="H79" s="61" t="n"/>
+      <c r="I79" s="60" t="inlineStr">
+        <is>
+          <t>Barométrico de alivio, contrapeso ajustable, cierre por gravedad</t>
+        </is>
+      </c>
+      <c r="J79" s="61" t="n"/>
+      <c r="K79" s="61" t="n"/>
+      <c r="L79" s="61" t="n"/>
+      <c r="M79" s="61" t="n"/>
+      <c r="N79" s="61" t="n"/>
+      <c r="O79" s="61" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="60" t="inlineStr">
+        <is>
+          <t>Rango de ajuste start-open</t>
+        </is>
+      </c>
+      <c r="B80" s="61" t="n"/>
+      <c r="C80" s="61" t="n"/>
+      <c r="D80" s="61" t="n"/>
+      <c r="E80" s="61" t="n"/>
+      <c r="F80" s="61" t="n"/>
+      <c r="G80" s="61" t="n"/>
+      <c r="H80" s="61" t="n"/>
+      <c r="I80" s="60" t="inlineStr">
+        <is>
+          <t>12-75 Pa (0.05-0.30 in c.a.), que cubre el set-point de +25 Pa</t>
+        </is>
+      </c>
+      <c r="J80" s="61" t="n"/>
+      <c r="K80" s="61" t="n"/>
+      <c r="L80" s="61" t="n"/>
+      <c r="M80" s="61" t="n"/>
+      <c r="N80" s="61" t="n"/>
+      <c r="O80" s="61" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="63" t="inlineStr">
-        <is>
-          <t>4.1. Si el cliente no dispone de PLC, se sustituye/complementa con Dwyer Photohelic 3000MR-00AV (indicador + 2 relés SPDT, rango 0-0.25 in c.a.; Northeast Controls (https://nciweb.net/pressure1.htm), consulta 2026-07-23), que genera las alarmas de la Tabla 1 de forma autónoma.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
+      <c r="A81" s="60" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="B81" s="61" t="n"/>
+      <c r="C81" s="61" t="n"/>
+      <c r="D81" s="61" t="n"/>
+      <c r="E81" s="61" t="n"/>
+      <c r="F81" s="61" t="n"/>
+      <c r="G81" s="61" t="n"/>
+      <c r="H81" s="61" t="n"/>
+      <c r="I81" s="60" t="inlineStr">
+        <is>
+          <t>Aluminio extruido 6063-T5 o línea severe-environment; galvanizado descartado</t>
+        </is>
+      </c>
+      <c r="J81" s="61" t="n"/>
+      <c r="K81" s="61" t="n"/>
+      <c r="L81" s="61" t="n"/>
+      <c r="M81" s="61" t="n"/>
+      <c r="N81" s="61" t="n"/>
+      <c r="O81" s="61" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="60" t="inlineStr">
+        <is>
+          <t>Dimensionamiento</t>
+        </is>
+      </c>
+      <c r="B82" s="61" t="n"/>
+      <c r="C82" s="61" t="n"/>
+      <c r="D82" s="61" t="n"/>
+      <c r="E82" s="61" t="n"/>
+      <c r="F82" s="61" t="n"/>
+      <c r="G82" s="61" t="n"/>
+      <c r="H82" s="61" t="n"/>
+      <c r="I82" s="60" t="inlineStr">
+        <is>
+          <t>Caudal de alivio de diseño con velocidad facial ≤ 2.5 m/s (dato típico); tamaño final por confirmar con proveedor</t>
+        </is>
+      </c>
+      <c r="J82" s="61" t="n"/>
+      <c r="K82" s="61" t="n"/>
+      <c r="L82" s="61" t="n"/>
+      <c r="M82" s="61" t="n"/>
+      <c r="N82" s="61" t="n"/>
+      <c r="O82" s="61" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="60" t="inlineStr">
+        <is>
+          <t>Ensayos</t>
+        </is>
+      </c>
+      <c r="B83" s="61" t="n"/>
+      <c r="C83" s="61" t="n"/>
+      <c r="D83" s="61" t="n"/>
+      <c r="E83" s="61" t="n"/>
+      <c r="F83" s="61" t="n"/>
+      <c r="G83" s="61" t="n"/>
+      <c r="H83" s="61" t="n"/>
+      <c r="I83" s="60" t="inlineStr">
+        <is>
+          <t>AMCA 500-D (caída de presión y fuga)</t>
+        </is>
+      </c>
+      <c r="J83" s="61" t="n"/>
+      <c r="K83" s="61" t="n"/>
+      <c r="L83" s="61" t="n"/>
+      <c r="M83" s="61" t="n"/>
+      <c r="N83" s="61" t="n"/>
+      <c r="O83" s="61" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="60" t="inlineStr">
+        <is>
+          <t>Calibración</t>
+        </is>
+      </c>
+      <c r="B84" s="61" t="n"/>
+      <c r="C84" s="61" t="n"/>
+      <c r="D84" s="61" t="n"/>
+      <c r="E84" s="61" t="n"/>
+      <c r="F84" s="61" t="n"/>
+      <c r="G84" s="61" t="n"/>
+      <c r="H84" s="61" t="n"/>
+      <c r="I84" s="60" t="inlineStr">
+        <is>
+          <t>En comisionamiento, con micromanómetro, a +25 Pa</t>
+        </is>
+      </c>
+      <c r="J84" s="61" t="n"/>
+      <c r="K84" s="61" t="n"/>
+      <c r="L84" s="61" t="n"/>
+      <c r="M84" s="61" t="n"/>
+      <c r="N84" s="61" t="n"/>
+      <c r="O84" s="61" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="60" t="inlineStr">
+        <is>
+          <t>Primera opción</t>
+        </is>
+      </c>
+      <c r="B85" s="61" t="n"/>
+      <c r="C85" s="61" t="n"/>
+      <c r="D85" s="61" t="n"/>
+      <c r="E85" s="61" t="n"/>
+      <c r="F85" s="61" t="n"/>
+      <c r="G85" s="61" t="n"/>
+      <c r="H85" s="61" t="n"/>
+      <c r="I85" s="60" t="inlineStr">
+        <is>
+          <t>Greenheck SEBR-10 (severe environment; rango 0.05-0.30 in c.a.) (submittal (PDF) (https://content.greenheck.com/public/DAMProd/Original/10002/SEBR10Series_submittal.pdf)); canal Greenheck en Bogotá</t>
+        </is>
+      </c>
+      <c r="J85" s="61" t="n"/>
+      <c r="K85" s="61" t="n"/>
+      <c r="L85" s="61" t="n"/>
+      <c r="M85" s="61" t="n"/>
+      <c r="N85" s="61" t="n"/>
+      <c r="O85" s="61" t="n"/>
+    </row>
     <row r="86">
-      <c r="A86" s="62" t="inlineStr">
-        <is>
-          <t>5. Damper de alivio barométrico (PDSV-001)</t>
-        </is>
-      </c>
+      <c r="A86" s="60" t="inlineStr">
+        <is>
+          <t>Alternativa</t>
+        </is>
+      </c>
+      <c r="B86" s="61" t="n"/>
+      <c r="C86" s="61" t="n"/>
+      <c r="D86" s="61" t="n"/>
+      <c r="E86" s="61" t="n"/>
+      <c r="F86" s="61" t="n"/>
+      <c r="G86" s="61" t="n"/>
+      <c r="H86" s="61" t="n"/>
+      <c r="I86" s="60" t="inlineStr">
+        <is>
+          <t>Ruskin CBD6/BD6 (aluminio 6063-T5, control hasta 0.25 in c.a.) (Ruskin BD6 (https://www.ruskin.com/model/bd6))</t>
+        </is>
+      </c>
+      <c r="J86" s="61" t="n"/>
+      <c r="K86" s="61" t="n"/>
+      <c r="L86" s="61" t="n"/>
+      <c r="M86" s="61" t="n"/>
+      <c r="N86" s="61" t="n"/>
+      <c r="O86" s="61" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="64" t="inlineStr">
-        <is>
-          <t>Tabla 4. Especificación y candidatos (consulta 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="59" t="inlineStr">
-        <is>
-          <t>Parámetro</t>
-        </is>
-      </c>
-      <c r="B88" s="59" t="inlineStr">
-        <is>
-          <t>Especificación / candidatos</t>
-        </is>
-      </c>
-      <c r="C88" s="59" t="n"/>
-      <c r="D88" s="59" t="n"/>
-      <c r="E88" s="59" t="n"/>
-      <c r="F88" s="59" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="60" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="B89" s="60" t="inlineStr">
-        <is>
-          <t>Barométrico de alivio, contrapeso ajustable, cierre por gravedad</t>
-        </is>
-      </c>
-      <c r="C89" s="61" t="n"/>
-      <c r="D89" s="61" t="n"/>
-      <c r="E89" s="61" t="n"/>
-      <c r="F89" s="61" t="n"/>
+      <c r="A87" s="60" t="inlineStr">
+        <is>
+          <t>Alternativa</t>
+        </is>
+      </c>
+      <c r="B87" s="61" t="n"/>
+      <c r="C87" s="61" t="n"/>
+      <c r="D87" s="61" t="n"/>
+      <c r="E87" s="61" t="n"/>
+      <c r="F87" s="61" t="n"/>
+      <c r="G87" s="61" t="n"/>
+      <c r="H87" s="61" t="n"/>
+      <c r="I87" s="60" t="inlineStr">
+        <is>
+          <t>Nailor 1390CB-EAF (contrapeso 360°, rodamientos de bolas para diferenciales muy bajos, opción aluminio) (submittal (PDF) (https://nailor.com/sites/default/files/documents/1390CB_B_0_0.pdf))</t>
+        </is>
+      </c>
+      <c r="J87" s="61" t="n"/>
+      <c r="K87" s="61" t="n"/>
+      <c r="L87" s="61" t="n"/>
+      <c r="M87" s="61" t="n"/>
+      <c r="N87" s="61" t="n"/>
+      <c r="O87" s="61" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="60" t="inlineStr">
-        <is>
-          <t>Rango de ajuste start-open</t>
-        </is>
-      </c>
-      <c r="B90" s="60" t="inlineStr">
-        <is>
-          <t>12-75 Pa (0.05-0.30 in c.a.), que cubre el set-point de +25 Pa</t>
-        </is>
-      </c>
-      <c r="C90" s="61" t="n"/>
-      <c r="D90" s="61" t="n"/>
-      <c r="E90" s="61" t="n"/>
-      <c r="F90" s="61" t="n"/>
+      <c r="A90" s="62" t="inlineStr">
+        <is>
+          <t>6. Tomas de impulso, montaje y accesorios</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="60" t="inlineStr">
-        <is>
-          <t>Materiales</t>
-        </is>
-      </c>
-      <c r="B91" s="60" t="inlineStr">
-        <is>
-          <t>Aluminio extruido 6063-T5 o línea severe-environment; galvanizado descartado</t>
-        </is>
-      </c>
-      <c r="C91" s="61" t="n"/>
-      <c r="D91" s="61" t="n"/>
-      <c r="E91" s="61" t="n"/>
-      <c r="F91" s="61" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="60" t="inlineStr">
-        <is>
-          <t>Dimensionamiento</t>
-        </is>
-      </c>
-      <c r="B92" s="60" t="inlineStr">
-        <is>
-          <t>Caudal de alivio de diseño con velocidad facial ≤ 2.5 m/s (dato típico); tamaño final por confirmar con proveedor</t>
-        </is>
-      </c>
-      <c r="C92" s="61" t="n"/>
-      <c r="D92" s="61" t="n"/>
-      <c r="E92" s="61" t="n"/>
-      <c r="F92" s="61" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="60" t="inlineStr">
-        <is>
-          <t>Ensayos</t>
-        </is>
-      </c>
-      <c r="B93" s="60" t="inlineStr">
-        <is>
-          <t>AMCA 500-D (caída de presión y fuga)</t>
-        </is>
-      </c>
-      <c r="C93" s="61" t="n"/>
-      <c r="D93" s="61" t="n"/>
-      <c r="E93" s="61" t="n"/>
-      <c r="F93" s="61" t="n"/>
-    </row>
+      <c r="A91" s="63" t="inlineStr">
+        <is>
+          <t>6.1. Toma de referencia exterior: caja estática de pared (tipo Dwyer A-417 o fabricación local inox 316, dato típico), orientada a sotavento, con purga o filtro de membrana por el ambiente clorado; tubería de impulso y conexiones 1/8 in NPT con sellante compatible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92"/>
+    <row r="93"/>
     <row r="94">
-      <c r="A94" s="60" t="inlineStr">
-        <is>
-          <t>Calibración</t>
-        </is>
-      </c>
-      <c r="B94" s="60" t="inlineStr">
-        <is>
-          <t>En comisionamiento, con micromanómetro, a +25 Pa</t>
-        </is>
-      </c>
-      <c r="C94" s="61" t="n"/>
-      <c r="D94" s="61" t="n"/>
-      <c r="E94" s="61" t="n"/>
-      <c r="F94" s="61" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="60" t="inlineStr">
-        <is>
-          <t>Primera opción</t>
-        </is>
-      </c>
-      <c r="B95" s="60" t="inlineStr">
-        <is>
-          <t>Greenheck SEBR-10 (severe environment; rango 0.05-0.30 in c.a.) (submittal (PDF) (https://content.greenheck.com/public/DAMProd/Original/10002/SEBR10Series_submittal.pdf)); canal Greenheck en Bogotá</t>
-        </is>
-      </c>
-      <c r="C95" s="61" t="n"/>
-      <c r="D95" s="61" t="n"/>
-      <c r="E95" s="61" t="n"/>
-      <c r="F95" s="61" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="60" t="inlineStr">
-        <is>
-          <t>Alternativa</t>
-        </is>
-      </c>
-      <c r="B96" s="60" t="inlineStr">
-        <is>
-          <t>Ruskin CBD6/BD6 (aluminio 6063-T5, control hasta 0.25 in c.a.) (Ruskin BD6 (https://www.ruskin.com/model/bd6))</t>
-        </is>
-      </c>
-      <c r="C96" s="61" t="n"/>
-      <c r="D96" s="61" t="n"/>
-      <c r="E96" s="61" t="n"/>
-      <c r="F96" s="61" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="60" t="inlineStr">
-        <is>
-          <t>Alternativa</t>
-        </is>
-      </c>
-      <c r="B97" s="60" t="inlineStr">
-        <is>
-          <t>Nailor 1390CB-EAF (contrapeso 360°, rodamientos de bolas para diferenciales muy bajos, opción aluminio) (submittal (PDF) (https://nailor.com/sites/default/files/documents/1390CB_B_0_0.pdf))</t>
-        </is>
-      </c>
-      <c r="C97" s="61" t="n"/>
-      <c r="D97" s="61" t="n"/>
-      <c r="E97" s="61" t="n"/>
-      <c r="F97" s="61" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="62" t="inlineStr">
-        <is>
-          <t>6. Tomas de impulso, montaje y accesorios</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="63" t="inlineStr">
-        <is>
-          <t>6.1. Toma de referencia exterior: caja estática de pared (tipo Dwyer A-417 o fabricación local inox 316, dato típico), orientada a sotavento, con purga o filtro de membrana por el ambiente clorado; tubería de impulso y conexiones 1/8 in NPT con sellante compatible.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A94" s="63" t="inlineStr">
+        <is>
+          <t>6.2. Los instrumentos (cuerpos de aluminio fundido) se instalan en el interior de la sala o en gabinete IP66 con prensaestopas niquelados/inox; los herrajes estándar zincados se reemplazan por soportes fabricados en inox 316. Cableado de la señal 4-20 mA apantallado; protecciones y tablero conforme a RETIE/NTC 2050 (listado_equipos.md, ítems 16-17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="98">
+      <c r="A98" s="62" t="inlineStr">
+        <is>
+          <t>7. Disponibilidad en Colombia</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="63" t="inlineStr">
+        <is>
+          <t>7.1. Dwyer: Vía Industrial (Bogotá/Cali, viaindustrial.com (https://www.viaindustrial.com/dwyer/marca/)), RS Importaciones y Suministros (Bogotá, rsimportacionesysuministros.com.co (https://rsimportacionesysuministros.com.co/producto/transmisor-magnehelic-dwyer-instruments-a/)), SICO Global (sico.global (https://sico.global/productos/transmisor-medidor-de-presion-diferencial-dwyer-magnehelic-605/)) — consulta 2026-07-23. Setra y los dampers Nailor/Ruskin se gestionan por importación o representante (por confirmar); Greenheck vía Prime Lines HVAC, Bogotá.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100"/>
+    <row r="101"/>
     <row r="102"/>
     <row r="103"/>
-    <row r="104"/>
     <row r="105">
-      <c r="A105" s="63" t="inlineStr">
-        <is>
-          <t>6.2. Los instrumentos (cuerpos de aluminio fundido) se instalan en el interior de la sala o en gabinete IP66 con prensaestopas niquelados/inox; los herrajes estándar zincados se reemplazan por soportes fabricados en inox 316. Cableado de la señal 4-20 mA apantallado; protecciones y tablero conforme a RETIE/NTC 2050 (listado_equipos.md, ítems 16-17).</t>
-        </is>
-      </c>
-    </row>
-    <row r="106"/>
+      <c r="A105" s="62" t="inlineStr">
+        <is>
+          <t>8. Normas aplicables</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="63" t="inlineStr">
+        <is>
+          <t>8.1. AMCA 500-D (damper), ASHRAE 62.1/170 (niveles de presurización de referencia), OSHA 29 CFR 1910.1450 (buena práctica de laboratorios), RETIE y NTC 2050 (instalación eléctrica e instrumentación), Resolución 0312 de 2019 (Colombia).</t>
+        </is>
+      </c>
+    </row>
     <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="111">
-      <c r="A111" s="62" t="inlineStr">
-        <is>
-          <t>7. Disponibilidad en Colombia</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="63" t="inlineStr">
-        <is>
-          <t>7.1. Dwyer: Vía Industrial (Bogotá/Cali, viaindustrial.com (https://www.viaindustrial.com/dwyer/marca/)), RS Importaciones y Suministros (Bogotá, rsimportacionesysuministros.com.co (https://rsimportacionesysuministros.com.co/producto/transmisor-magnehelic-dwyer-instruments-a/)), SICO Global (sico.global (https://sico.global/productos/transmisor-medidor-de-presion-diferencial-dwyer-magnehelic-605/)) — consulta 2026-07-23. Setra y los dampers Nailor/Ruskin se gestionan por importación o representante (por confirmar); Greenheck vía Prime Lines HVAC, Bogotá.</t>
-        </is>
-      </c>
-    </row>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="120">
-      <c r="A120" s="62" t="inlineStr">
-        <is>
-          <t>8. Normas aplicables</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="63" t="inlineStr">
-        <is>
-          <t>8.1. AMCA 500-D (damper), ASHRAE 62.1/170 (niveles de presurización de referencia), OSHA 29 CFR 1910.1450 (buena práctica de laboratorios), RETIE y NTC 2050 (instalación eléctrica e instrumentación), Resolución 0312 de 2019 (Colombia).</t>
-        </is>
-      </c>
-    </row>
-    <row r="122"/>
-    <row r="123"/>
   </sheetData>
-  <mergeCells count="67">
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="C48:F48"/>
-    <mergeCell ref="B91:F91"/>
-    <mergeCell ref="A81:F84"/>
-    <mergeCell ref="B62:F62"/>
-    <mergeCell ref="A19:F22"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B66:F66"/>
-    <mergeCell ref="A120:F120"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="B93:F93"/>
-    <mergeCell ref="A86:F86"/>
-    <mergeCell ref="B96:F96"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B77:F77"/>
+  <mergeCells count="111">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="I52:O52"/>
+    <mergeCell ref="A83:H83"/>
+    <mergeCell ref="I83:O83"/>
     <mergeCell ref="N3:O3"/>
-    <mergeCell ref="C49:F49"/>
-    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="A99:O103"/>
+    <mergeCell ref="A69:H69"/>
+    <mergeCell ref="I69:O69"/>
+    <mergeCell ref="I84:O84"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="K41:O41"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="I86:O86"/>
+    <mergeCell ref="C2:L3"/>
+    <mergeCell ref="I80:O80"/>
+    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A86:H86"/>
+    <mergeCell ref="K43:O43"/>
+    <mergeCell ref="I70:O70"/>
+    <mergeCell ref="A72:O74"/>
+    <mergeCell ref="I57:O57"/>
+    <mergeCell ref="I54:O54"/>
+    <mergeCell ref="F39:J39"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A81:H81"/>
+    <mergeCell ref="I56:O56"/>
+    <mergeCell ref="I87:O87"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="B1:B5"/>
+    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="A67:H67"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A82:H82"/>
+    <mergeCell ref="I82:O82"/>
+    <mergeCell ref="A30:O36"/>
+    <mergeCell ref="I10:O10"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="I59:O59"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="A105:F109"/>
-    <mergeCell ref="B60:F60"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B61:F61"/>
-    <mergeCell ref="A25:F33"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="A100:F100"/>
-    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="F41:J41"/>
+    <mergeCell ref="A84:H84"/>
+    <mergeCell ref="A62:O62"/>
+    <mergeCell ref="K40:O40"/>
+    <mergeCell ref="I11:O11"/>
+    <mergeCell ref="A85:H85"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A98:O98"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="A45:O47"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A90:O90"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="I64:O64"/>
+    <mergeCell ref="I79:O79"/>
+    <mergeCell ref="A106:O107"/>
+    <mergeCell ref="I51:O51"/>
+    <mergeCell ref="A79:H79"/>
+    <mergeCell ref="F40:J40"/>
+    <mergeCell ref="A70:H70"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A76:O76"/>
+    <mergeCell ref="I65:O65"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A24:O29"/>
+    <mergeCell ref="A91:O93"/>
+    <mergeCell ref="F38:J38"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="I85:O85"/>
+    <mergeCell ref="A1:A5"/>
+    <mergeCell ref="A9:O9"/>
+    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="K39:O39"/>
+    <mergeCell ref="I66:O66"/>
+    <mergeCell ref="A19:O21"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="I53:O53"/>
+    <mergeCell ref="K38:O38"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="I12:O12"/>
+    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="I68:O68"/>
+    <mergeCell ref="I55:O55"/>
+    <mergeCell ref="I67:O67"/>
+    <mergeCell ref="I14:O14"/>
+    <mergeCell ref="A94:O96"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="I78:O78"/>
+    <mergeCell ref="I13:O13"/>
+    <mergeCell ref="A105:O105"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="A87:H87"/>
+    <mergeCell ref="A65:H65"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="F42:J42"/>
+    <mergeCell ref="I15:O15"/>
+    <mergeCell ref="A23:O23"/>
+    <mergeCell ref="I81:O81"/>
+    <mergeCell ref="A80:H80"/>
     <mergeCell ref="N1:O1"/>
-    <mergeCell ref="A34:F43"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B88:F88"/>
-    <mergeCell ref="C2:L3"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="C45:F45"/>
-    <mergeCell ref="A121:F123"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A111:F111"/>
-    <mergeCell ref="A58:F58"/>
-    <mergeCell ref="C47:F47"/>
-    <mergeCell ref="A1:A5"/>
-    <mergeCell ref="C50:F50"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B92:F92"/>
-    <mergeCell ref="A52:F56"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="B65:F65"/>
-    <mergeCell ref="B68:F68"/>
-    <mergeCell ref="C1:L1"/>
-    <mergeCell ref="A112:F118"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="K42:O42"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="F43:J43"/>
     <mergeCell ref="C4:L6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="B76:F76"/>
-    <mergeCell ref="B94:F94"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="A101:F104"/>
-    <mergeCell ref="B79:F79"/>
-    <mergeCell ref="B1:B5"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="I58:O58"/>
+    <mergeCell ref="A49:O49"/>
+    <mergeCell ref="A52:H52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
